--- a/astro-site/public/dl/plan-negocio-cocteleria-eventos/calculadora-pricing-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-cocteleria-eventos/calculadora-pricing-eventos.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculadora" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ejemplos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ejemplos'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0 €"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="#,##0 €"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11">
@@ -150,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -163,48 +165,75 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -570,9 +599,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:F39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -597,6 +626,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -623,7 +653,7 @@
           <t>Coste bebida basica por invitado/hora</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="22" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -641,7 +671,7 @@
           <t>Coste bebida media por invitado/hora</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="22" t="n">
         <v>4</v>
       </c>
     </row>
@@ -661,7 +691,7 @@
           <t>Coste bebida premium por invitado/hora</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="22" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -679,7 +709,7 @@
           <t>Tarifa bartender freelance por hora</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="22" t="n">
         <v>22</v>
       </c>
     </row>
@@ -697,7 +727,7 @@
           <t>Tarifa runner por hora</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="22" t="n">
         <v>12</v>
       </c>
     </row>
@@ -715,7 +745,7 @@
           <t>Coste consumibles por invitado</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="22" t="n">
         <v>1.2</v>
       </c>
     </row>
@@ -733,7 +763,7 @@
           <t>Coste hielo por invitado</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="22" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -753,7 +783,7 @@
           <t>Coste combustible por km</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="22" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -763,7 +793,7 @@
           <t>Coste decoracion tematica especial (EUR)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="23" t="n">
         <v>150</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -775,6 +805,7 @@
         <v>0.12</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
         <is>
@@ -788,9 +819,9 @@
           <t>Coste bebidas</t>
         </is>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="24">
         <f>C5*C6*IF(C8=1,F5,IF(C8=2,F6,F7))</f>
-        <v/>
+        <v>2000.0</v>
       </c>
     </row>
     <row r="17">
@@ -799,9 +830,9 @@
           <t>Coste bartenders adicionales</t>
         </is>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="24">
         <f>C9*F8*C6</f>
-        <v/>
+        <v>110.0</v>
       </c>
     </row>
     <row r="18">
@@ -810,9 +841,9 @@
           <t>Coste runners</t>
         </is>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="24">
         <f>C10*F9*C6</f>
-        <v/>
+        <v>60.0</v>
       </c>
     </row>
     <row r="19">
@@ -821,9 +852,9 @@
           <t>Coste consumibles</t>
         </is>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="24">
         <f>C5*F10</f>
-        <v/>
+        <v>120.0</v>
       </c>
     </row>
     <row r="20">
@@ -832,9 +863,9 @@
           <t>Coste hielo</t>
         </is>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="24">
         <f>C5*F11</f>
-        <v/>
+        <v>40.0</v>
       </c>
     </row>
     <row r="21">
@@ -843,9 +874,9 @@
           <t>Coste combustible (ida + vuelta)</t>
         </is>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="24">
         <f>C11*2*F12</f>
-        <v/>
+        <v>20.0</v>
       </c>
     </row>
     <row r="22">
@@ -854,9 +885,9 @@
           <t>Coste decoracion tematica</t>
         </is>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="24">
         <f>C13</f>
-        <v/>
+        <v>150.0</v>
       </c>
     </row>
     <row r="23">
@@ -865,11 +896,12 @@
           <t>TOTAL COSTE BRUTO EVENTO</t>
         </is>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="25">
         <f>SUM(F16:F22)</f>
-        <v/>
-      </c>
-    </row>
+        <v>2500.0</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="9" t="inlineStr">
         <is>
@@ -883,9 +915,9 @@
           <t>PRECIO MINIMO (margen 35%, sin comision WP)</t>
         </is>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="26">
         <f>F23/(1-0.35)</f>
-        <v/>
+        <v>3846.153846153846</v>
       </c>
     </row>
     <row r="27">
@@ -894,9 +926,9 @@
           <t>PRECIO RECOMENDADO (margen 45%)</t>
         </is>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="27">
         <f>IF(C12="S",(F23/(1-0.45))/(1-F13),F23/(1-0.45))</f>
-        <v/>
+        <v>5165.289256198346</v>
       </c>
     </row>
     <row r="28">
@@ -905,20 +937,21 @@
           <t>PRECIO PREMIUM (margen 55%, posicionamiento alto)</t>
         </is>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="26">
         <f>IF(C12="S",(F23/(1-0.55))/(1-F13),F23/(1-0.55))</f>
-        <v/>
-      </c>
-    </row>
+        <v>6313.131313131314</v>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
           <t>PRECIO POR INVITADO (sobre precio recomendado)</t>
         </is>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="28">
         <f>F27/C5</f>
-        <v/>
+        <v>51.652892561983464</v>
       </c>
     </row>
     <row r="31">
@@ -927,11 +960,12 @@
           <t>Margen neto sobre precio recomendado</t>
         </is>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="26">
         <f>IF(C12="S",F27-F23-F27*F13,F27-F23)</f>
-        <v/>
-      </c>
-    </row>
+        <v>2045.4545454545446</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="11" t="inlineStr">
         <is>
@@ -983,34 +1017,43 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B26:E26"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B19:E19"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B19:E19"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1018,7 +1061,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1047,6 +1090,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -1106,13 +1150,13 @@
           <t>5h</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n">
+      <c r="E5" s="29" t="n">
         <v>410</v>
       </c>
-      <c r="F5" s="20" t="n">
+      <c r="F5" s="29" t="n">
         <v>870</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="30" t="n">
         <v>17.4</v>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -1138,13 +1182,13 @@
           <t>5h</t>
         </is>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="29" t="n">
         <v>805</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="29" t="n">
         <v>1670</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="30" t="n">
         <v>16.7</v>
       </c>
       <c r="H6" s="19" t="inlineStr">
@@ -1170,13 +1214,13 @@
           <t>6h</t>
         </is>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="29" t="n">
         <v>1530</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="29" t="n">
         <v>3450</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="30" t="n">
         <v>23</v>
       </c>
       <c r="H7" s="19" t="inlineStr">
@@ -1202,13 +1246,13 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="29" t="n">
         <v>720</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="29" t="n">
         <v>1310</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="30" t="n">
         <v>16.4</v>
       </c>
       <c r="H8" s="19" t="inlineStr">
@@ -1234,13 +1278,13 @@
           <t>5h</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="29" t="n">
         <v>2010</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="29" t="n">
         <v>3650</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="30" t="n">
         <v>18.3</v>
       </c>
       <c r="H9" s="19" t="inlineStr">
@@ -1266,13 +1310,13 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="29" t="n">
         <v>295</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="29" t="n">
         <v>540</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="30" t="n">
         <v>18</v>
       </c>
       <c r="H10" s="19" t="inlineStr">
@@ -1298,13 +1342,13 @@
           <t>3h</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="29" t="n">
         <v>220</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="29" t="n">
         <v>400</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="30" t="n">
         <v>16</v>
       </c>
       <c r="H11" s="19" t="inlineStr">
@@ -1330,13 +1374,13 @@
           <t>3h</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="29" t="n">
         <v>480</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="29" t="n">
         <v>870</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="30" t="n">
         <v>14.5</v>
       </c>
       <c r="H12" s="19" t="inlineStr">
@@ -1362,13 +1406,13 @@
           <t>5h</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="29" t="n">
         <v>1080</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="29" t="n">
         <v>1965</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="30" t="n">
         <v>16.4</v>
       </c>
       <c r="H13" s="19" t="inlineStr">
@@ -1394,13 +1438,13 @@
           <t>4h</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="29" t="n">
         <v>380</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="29" t="n">
         <v>690</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="30" t="n">
         <v>17.3</v>
       </c>
       <c r="H14" s="19" t="inlineStr">
@@ -1414,6 +1458,15 @@
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>